--- a/data/trans_dic/P5B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Provincia-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia</t>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -638,7 +639,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -653,7 +654,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -693,7 +694,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -716,69 +717,69 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,33</t>
+          <t>1,09; 10,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,23</t>
+          <t>0,0; 13,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,03</t>
+          <t>0,0; 5,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,98</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 19,16</t>
+          <t>1,55; 16,07</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,66; 15,21</t>
+          <t>2,6; 15,9</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,95</t>
+          <t>0,52; 4,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 11,49</t>
+          <t>1,63; 12,19</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,65; 8,93</t>
+          <t>1,63; 8,18</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,96</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -843,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,09%</t>
         </is>
       </c>
     </row>
@@ -856,69 +857,69 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 10,65</t>
+          <t>0,99; 10,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,25</t>
+          <t>1,27; 11,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,85</t>
+          <t>1,57; 8,82</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 61,18</t>
+          <t>0,8; 63,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,52</t>
+          <t>0,0; 6,84</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,15</t>
+          <t>2,18; 11,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,25</t>
+          <t>0,0; 5,52</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,22</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,38; 6,65</t>
+          <t>1,34; 6,45</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 9,72</t>
+          <t>2,37; 9,44</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,75</t>
+          <t>1,12; 5,05</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 41,73</t>
+          <t>0,35; 45,66</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,16; 11,64</t>
+          <t>2,14; 12,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,24</t>
+          <t>0,0; 9,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,0</t>
+          <t>0,0; 7,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,24</t>
+          <t>1,82; 10,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,2</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,23</t>
+          <t>0,81; 7,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,49; 8,46</t>
+          <t>2,51; 9,15</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,22</t>
+          <t>0,0; 3,48</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,45</t>
+          <t>0,86; 4,97</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1079,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1098,7 +1099,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1118,7 +1119,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,27</t>
+          <t>0,0; 5,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,12</t>
+          <t>0,0; 10,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,66</t>
+          <t>0,0; 9,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,53</t>
+          <t>1,62; 8,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0; 2,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,21</t>
+          <t>0,0; 8,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,08; 11,02</t>
+          <t>1,16; 11,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,28; 5,71</t>
+          <t>1,3; 6,0</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,84</t>
+          <t>0,0; 4,87</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,63; 6,21</t>
+          <t>0,64; 6,36</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 6,05</t>
+          <t>0,66; 5,66</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 57,9</t>
+          <t>7,2; 51,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,83</t>
+          <t>0,0; 21,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,93</t>
+          <t>0,0; 9,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,37</t>
+          <t>0,0; 30,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,61; 22,39</t>
+          <t>2,59; 21,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,8</t>
+          <t>0,0; 8,74</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 6,15</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,34; 30,2</t>
+          <t>3,38; 30,21</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,5</t>
+          <t>1,74; 15,67</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,62</t>
+          <t>0,0; 6,49</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1416,69 +1417,69 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,77</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,74</t>
+          <t>0,0; 9,35</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 7,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 1,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,12</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 2,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,61</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1498,7 +1499,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1523,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1538,12 +1539,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,31; 7,77</t>
+          <t>1,32; 7,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 4,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 5,53</t>
+          <t>1,0; 6,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,45</t>
+          <t>0,0; 3,28</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,02</t>
+          <t>1,81; 8,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,11</t>
+          <t>0,0; 3,03</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,62</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 3,81</t>
+          <t>0,36; 4,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,47</t>
+          <t>2,24; 6,59</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,62</t>
+          <t>0,28; 2,34</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,38</t>
+          <t>0,55; 3,43</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,12</t>
+          <t>0,53; 3,04</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1634,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1696,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 8,29</t>
+          <t>1,39; 8,49</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,33</t>
+          <t>0,0; 3,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,45</t>
+          <t>1,2; 7,25</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0; 1,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0; 0,91</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,26</t>
+          <t>0,0; 3,31</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,76; 6,34</t>
+          <t>1,77; 6,25</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,55</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 1,39</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,78</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
     </row>
@@ -1773,49 +1774,49 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>1,79%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>4,7%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>3,41%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>1,78%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
@@ -1823,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -1836,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,46</t>
+          <t>2,55; 5,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,13</t>
+          <t>1,13; 3,17</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,02; 2,77</t>
+          <t>1,07; 2,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,51; 19,72</t>
+          <t>0,5; 16,58</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,41</t>
+          <t>1,91; 4,3</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,59</t>
+          <t>0,84; 2,67</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,58; 2,03</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,11</t>
+          <t>0,69; 2,24</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,31</t>
+          <t>2,64; 4,5</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,12; 2,54</t>
+          <t>1,14; 2,58</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,11</t>
+          <t>0,93; 2,08</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,87; 9,57</t>
+          <t>0,89; 9,47</t>
         </is>
       </c>
     </row>
@@ -1920,4 +1921,2040 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N31"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con calidad medioambiental mala o muy mala en la zona de residencia (tasa de respuesta: 99,82%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Almería</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>469</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>1780</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>3400</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>4079</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>519; 5057</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3286</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2438</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>591; 6118</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>1350; 8268</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>514; 4713</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1024; 7671</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>1585; 7963</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Cádiz</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2953</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2760</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2939</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>28229</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4178</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>6042</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3609</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>28229</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>674; 7136</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>688; 6278</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>1109; 6234</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1016; 81689</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4444</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1284; 6730</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4418</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1785; 8573</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2687; 10689</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>1688; 7604</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>897; 116231</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>3641</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1778</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6756</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>787</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>1388; 8078</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4889</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4259</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>1235; 6874</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>546; 5255</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3327; 12131</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3915</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1083; 6238</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Granada</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1431</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1413</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>3485</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>4271</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1431</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2176</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>3485</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3893</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5185</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4266</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>1188; 6507</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3758</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>910; 8810</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>1815; 8368</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5122</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>578; 5791</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>982; 8387</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Huelva</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2098</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>746</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2803</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>2738</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>1239</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>486</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>687; 4939</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3217</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3522</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>638; 5355</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3104</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2504</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>707; 6326</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>743; 6686</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4406</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2544</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>Jaén</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>726</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>0; 4164</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3498</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3708</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3023</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Málaga</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>4328</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>1423</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1251</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2487</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>8928</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3761</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>3739</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>1463; 8642</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4978</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>1165; 7331</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4087</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2004; 9221</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3687</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3280</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>558; 7195</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>4969; 14595</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>667; 5584</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>1294; 8070</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>1477; 8510</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n"/>
+      <c r="B26" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>3332</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>6478</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>768</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n"/>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>1254; 7657</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3598</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3220</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>1164; 7004</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5191</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>3309; 11670</t>
+        </is>
+      </c>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>0; 5237</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>0; 3750</t>
+        </is>
+      </c>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>0; 4850</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n"/>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>19275</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>9636</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>31282</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>9741</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>35195</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>17986</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>15655</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>41023</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n"/>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>12821; 26356</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>5359; 15093</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>5589; 15446</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>3343; 110326</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>10112; 22704</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>4495; 14371</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>3294; 11606</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>5221; 17062</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>27284; 46386</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>11532; 26127</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>10137; 22690</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>12694; 134992</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A25:A27"/>
+    <mergeCell ref="A28:A30"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P5B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Provincia-trans_dic.xlsx
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 10,6</t>
+          <t>1,08; 10,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,22</t>
+          <t>0,0; 13,82</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,37</t>
+          <t>0,0; 5,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -742,12 +742,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,55; 16,07</t>
+          <t>1,61; 18,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,6; 15,9</t>
+          <t>2,48; 15,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 4,77</t>
+          <t>0,52; 5,03</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 12,19</t>
+          <t>1,6; 11,76</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 8,18</t>
+          <t>1,53; 8,37</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -857,37 +857,37 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 10,51</t>
+          <t>0,99; 11,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,27; 11,54</t>
+          <t>1,29; 12,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 8,82</t>
+          <t>1,58; 8,64</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,8; 63,99</t>
+          <t>0,79; 65,34</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,84</t>
+          <t>0,0; 6,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 11,43</t>
+          <t>2,2; 12,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,52</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,22 +897,22 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,45</t>
+          <t>1,24; 7,06</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,37; 9,44</t>
+          <t>2,92; 9,51</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,12; 5,05</t>
+          <t>0,88; 5,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 45,66</t>
+          <t>0,34; 40,75</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 12,49</t>
+          <t>2,13; 12,13</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,27</t>
+          <t>0,0; 10,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,31</t>
+          <t>0,0; 7,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 10,12</t>
+          <t>1,81; 9,68</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 7,82</t>
+          <t>0,8; 7,44</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,51; 9,15</t>
+          <t>2,52; 8,9</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,48</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 4,97</t>
+          <t>0,92; 5,14</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,89</t>
+          <t>0,0; 6,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,44</t>
+          <t>0,0; 10,41</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,69</t>
+          <t>0,0; 10,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1157,7 +1157,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,85</t>
+          <t>1,62; 9,4</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1167,32 +1167,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,0</t>
+          <t>0,0; 6,7</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,28</t>
+          <t>1,16; 11,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,3; 6,0</t>
+          <t>1,29; 6,21</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,87</t>
+          <t>0,0; 5,13</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,36</t>
+          <t>0,64; 6,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,66</t>
+          <t>0,66; 5,73</t>
         </is>
       </c>
     </row>
@@ -1277,17 +1277,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 51,77</t>
+          <t>7,2; 50,65</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,26</t>
+          <t>0,0; 21,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,94</t>
+          <t>0,0; 11,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1297,42 +1297,42 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,9</t>
+          <t>0,0; 25,26</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,59; 21,74</t>
+          <t>2,53; 21,5</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,74</t>
+          <t>0,0; 8,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,15</t>
+          <t>0,0; 6,17</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,38; 30,21</t>
+          <t>3,36; 27,14</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,74; 15,67</t>
+          <t>1,55; 14,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,49</t>
+          <t>0,0; 6,37</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,38</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,35</t>
+          <t>0,0; 8,11</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,58</t>
+          <t>0,0; 6,8</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,94</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,95</t>
+          <t>0,0; 2,75</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,81</t>
+          <t>1,32; 7,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,27</t>
+          <t>0,0; 4,29</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,31</t>
+          <t>1,01; 5,56</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,28</t>
+          <t>0,0; 3,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,81; 8,32</t>
+          <t>1,76; 8,16</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,03</t>
+          <t>0,0; 2,8</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 3,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,64</t>
+          <t>0,39; 4,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 6,59</t>
+          <t>2,18; 6,65</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,34</t>
+          <t>0,28; 2,38</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,43</t>
+          <t>0,73; 3,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,04</t>
+          <t>0,42; 3,02</t>
         </is>
       </c>
     </row>
@@ -1697,17 +1697,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,39; 8,49</t>
+          <t>1,25; 7,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,13</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>0,0; 3,1</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,2; 7,25</t>
+          <t>1,22; 7,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1732,27 +1732,27 @@
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,31</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,77; 6,25</t>
+          <t>1,71; 6,07</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,39</t>
+          <t>0,0; 1,76</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 2,0</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,55; 5,24</t>
+          <t>2,7; 5,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,17</t>
+          <t>1,09; 3,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,07; 2,95</t>
+          <t>1,04; 2,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,5; 16,58</t>
+          <t>0,49; 18,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,3</t>
+          <t>2,0; 4,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,84; 2,67</t>
+          <t>0,86; 2,62</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,03</t>
+          <t>0,55; 2,07</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,24</t>
+          <t>0,74; 2,11</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,64; 4,5</t>
+          <t>2,58; 4,33</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,58</t>
+          <t>1,19; 2,66</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,08</t>
+          <t>0,91; 2,01</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 9,47</t>
+          <t>0,89; 10,9</t>
         </is>
       </c>
     </row>
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>519; 5057</t>
+          <t>515; 4985</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3286</t>
+          <t>0; 3436</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2438</t>
+          <t>0; 2454</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2234,12 +2234,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>591; 6118</t>
+          <t>614; 7114</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1350; 8268</t>
+          <t>1287; 7930</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>514; 4713</t>
+          <t>515; 4971</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1024; 7671</t>
+          <t>1008; 7404</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1585; 7963</t>
+          <t>1486; 8155</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2417,37 +2417,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>674; 7136</t>
+          <t>674; 7543</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>688; 6278</t>
+          <t>703; 6929</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1109; 6234</t>
+          <t>1120; 6111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1016; 81689</t>
+          <t>1012; 83411</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4444</t>
+          <t>0; 4155</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1284; 6730</t>
+          <t>1295; 7203</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4418</t>
+          <t>0; 3560</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -2457,22 +2457,22 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1785; 8573</t>
+          <t>1653; 9383</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2687; 10689</t>
+          <t>3307; 10771</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1688; 7604</t>
+          <t>1321; 7639</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>897; 116231</t>
+          <t>874; 103726</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1388; 8078</t>
+          <t>1376; 7846</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4889</t>
+          <t>0; 5425</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,12 +2640,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4259</t>
+          <t>0; 4454</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1235; 6874</t>
+          <t>1229; 6570</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>546; 5255</t>
+          <t>541; 4999</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3327; 12131</t>
+          <t>3343; 11805</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3915</t>
+          <t>0; 3899</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1083; 6238</t>
+          <t>1155; 6444</t>
         </is>
       </c>
     </row>
@@ -2833,17 +2833,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3893</t>
+          <t>0; 4104</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5185</t>
+          <t>0; 5171</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4266</t>
+          <t>0; 4544</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1188; 6507</t>
+          <t>1194; 6909</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -2863,32 +2863,32 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3758</t>
+          <t>0; 3148</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>910; 8810</t>
+          <t>903; 9353</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1815; 8368</t>
+          <t>1802; 8666</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5122</t>
+          <t>0; 5395</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>578; 5791</t>
+          <t>583; 5612</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>982; 8387</t>
+          <t>984; 8493</t>
         </is>
       </c>
     </row>
@@ -3041,17 +3041,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>687; 4939</t>
+          <t>687; 4833</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 3846</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3217</t>
+          <t>0; 3652</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -3061,42 +3061,42 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3522</t>
+          <t>0; 2879</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>638; 5355</t>
+          <t>624; 5295</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3104</t>
+          <t>0; 3131</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2504</t>
+          <t>0; 2512</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>707; 6326</t>
+          <t>704; 5683</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>743; 6686</t>
+          <t>664; 6287</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4406</t>
+          <t>0; 4323</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2544</t>
+          <t>0; 2225</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4164</t>
+          <t>0; 3613</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3498</t>
+          <t>0; 3138</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3708</t>
+          <t>0; 3500</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 3023</t>
+          <t>0; 2810</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1463; 8642</t>
+          <t>1464; 8678</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 4978</t>
+          <t>0; 5005</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1165; 7331</t>
+          <t>1173; 6451</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4087</t>
+          <t>0; 4307</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2004; 9221</t>
+          <t>1946; 9041</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3687</t>
+          <t>0; 3416</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3280</t>
+          <t>0; 3829</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>558; 7195</t>
+          <t>599; 6701</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4969; 14595</t>
+          <t>4827; 14733</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>667; 5584</t>
+          <t>672; 5687</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1294; 8070</t>
+          <t>1720; 7853</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1477; 8510</t>
+          <t>1173; 8453</t>
         </is>
       </c>
     </row>
@@ -3665,17 +3665,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1254; 7657</t>
+          <t>1123; 7021</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3598</t>
+          <t>0; 3852</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 3220</t>
+          <t>0; 4016</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3685,7 +3685,7 @@
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1164; 7004</t>
+          <t>1181; 7197</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -3700,27 +3700,27 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5191</t>
+          <t>0; 5686</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3309; 11670</t>
+          <t>3185; 11339</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 5237</t>
+          <t>0; 4130</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 3750</t>
+          <t>0; 4731</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 4850</t>
+          <t>0; 5764</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>12821; 26356</t>
+          <t>13613; 28203</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5359; 15093</t>
+          <t>5181; 16126</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5589; 15446</t>
+          <t>5434; 15144</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3343; 110326</t>
+          <t>3260; 121356</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10112; 22704</t>
+          <t>10573; 23863</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4495; 14371</t>
+          <t>4595; 14072</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3294; 11606</t>
+          <t>3152; 11816</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5221; 17062</t>
+          <t>5599; 16017</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>27284; 46386</t>
+          <t>26612; 44725</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>11532; 26127</t>
+          <t>12034; 26919</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>10137; 22690</t>
+          <t>9970; 22026</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12694; 134992</t>
+          <t>12678; 155409</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P5B_R-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P5B_R-Provincia-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,37 +649,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6,31%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>4,01%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,03%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>6,31%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,08; 10,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,82</t>
+          <t>1,6; 19,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,41</t>
+          <t>2,66; 15,21</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,17 +737,17 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,08; 10,33</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,61; 18,68</t>
+          <t>0,0; 12,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 15,25</t>
+          <t>0,0; 6,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -757,17 +757,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,52; 5,03</t>
+          <t>0,52; 4,95</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,6; 11,76</t>
+          <t>2,2; 12,01</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,53; 8,37</t>
+          <t>1,65; 8,93</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5,57%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,84%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>4,35%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>5,07%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>4,16%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>22,11%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 11,11</t>
+          <t>0,0; 6,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,29; 12,74</t>
+          <t>2,2; 12,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,58; 8,64</t>
+          <t>0,0; 4,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,79; 65,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,4</t>
+          <t>1,0; 10,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 12,23</t>
+          <t>1,27; 11,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>1,62; 8,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,7; 15,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,24; 7,06</t>
+          <t>1,38; 6,65</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,92; 9,51</t>
+          <t>2,39; 9,72</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,07</t>
+          <t>0,83; 4,75</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 40,75</t>
+          <t>0,17; 7,25</t>
         </is>
       </c>
     </row>
@@ -929,62 +929,62 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2,58%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>5,63%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>1,49%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5,1%</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5,1%</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 12,13</t>
+          <t>1,81; 9,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,29</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,17 +1012,17 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,64</t>
+          <t>0,75; 7,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 9,68</t>
+          <t>2,16; 11,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,24</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,17 +1032,17 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 7,44</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,52; 8,9</t>
+          <t>2,49; 8,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,0; 3,22</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,14</t>
+          <t>0,8; 5,28</t>
         </is>
       </c>
     </row>
@@ -1069,44 +1069,44 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1,63%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,76%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1,73%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,88%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>3,21%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4,46%</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3,06%</t>
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,21</t>
+          <t>1,62; 9,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,32</t>
+          <t>0,0; 8,24</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,19; 11,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 9,4</t>
+          <t>0,0; 5,27</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 9,12</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,7</t>
+          <t>0,0; 10,75</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,16; 11,97</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,29; 6,21</t>
+          <t>1,28; 5,71</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,13</t>
+          <t>0,0; 4,84</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 6,17</t>
+          <t>0,64; 6,62</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,66; 5,73</t>
+          <t>0,68; 6,44</t>
         </is>
       </c>
     </row>
@@ -1209,44 +1209,44 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>6,18%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>1,72%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>21,99%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,14%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="J12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>6,18%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,09%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
           <t>13,39%</t>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,64%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,2; 50,65</t>
+          <t>0,0; 25,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,32</t>
+          <t>2,61; 22,39</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,28</t>
+          <t>0,0; 9,8</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,26</t>
+          <t>7,2; 57,9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 21,5</t>
+          <t>0,0; 20,83</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,81</t>
+          <t>0,0; 9,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,17</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,36; 27,14</t>
+          <t>3,34; 30,2</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,55; 14,73</t>
+          <t>1,55; 14,5</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,37</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,96</t>
+          <t>0,0; 3,2</t>
         </is>
       </c>
     </row>
@@ -1354,57 +1354,57 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,65%</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,8</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1462,7 +1462,7 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,72</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 3,94</t>
         </is>
       </c>
     </row>
@@ -1489,62 +1489,62 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>4,15%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>1,68%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,22%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2,68%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,15%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>4,03%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
           <t>1,6%</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>4,03%</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0,88%</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,42%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,84</t>
+          <t>1,76; 8,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,29</t>
+          <t>0,0; 3,11</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,01; 5,56</t>
+          <t>0,0; 3,62</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,46</t>
+          <t>0,34; 4,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,16</t>
+          <t>1,31; 7,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,8</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,21</t>
+          <t>0,99; 5,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 4,32</t>
+          <t>0,0; 4,01</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,18; 6,65</t>
+          <t>2,18; 6,47</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,38</t>
+          <t>0,28; 2,62</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,34</t>
+          <t>0,74; 3,49</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,42; 3,02</t>
+          <t>0,53; 3,15</t>
         </is>
       </c>
     </row>
@@ -1629,44 +1629,44 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>3,26%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
           <t>3,7%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>0,67%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="I18" s="2" t="inlineStr">
         <is>
           <t>0,61%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="J18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>0,96%</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
           <t>3,47%</t>
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,25; 7,79</t>
+          <t>1,21; 7,45</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,29</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1,38; 8,29</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>0,0; 3,36</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 3,1</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,22; 7,45</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 2,96</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,63</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,71; 6,07</t>
+          <t>1,76; 6,34</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,76</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,0</t>
+          <t>0,0; 1,78</t>
         </is>
       </c>
     </row>
@@ -1769,42 +1769,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,7; 5,6</t>
+          <t>1,86; 4,41</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1,09; 3,39</t>
+          <t>0,88; 2,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1,04; 2,9</t>
+          <t>0,55; 2,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0,49; 18,24</t>
+          <t>0,71; 2,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,51</t>
+          <t>2,59; 5,46</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,62</t>
+          <t>1,18; 3,31</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,07</t>
+          <t>1,02; 2,82</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,11</t>
+          <t>0,5; 2,85</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,33</t>
+          <t>2,53; 4,31</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,66</t>
+          <t>1,21; 2,5</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,01</t>
+          <t>0,91; 2,1</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0,89; 10,9</t>
+          <t>0,75; 2,07</t>
         </is>
       </c>
     </row>
@@ -1957,7 +1957,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1965,7 +1965,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -2073,37 +2073,37 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2141,37 +2141,37 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>2403</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3610</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>1780</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>997</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>469</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2403</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>3610</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2209,17 +2209,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>515; 4985</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3436</t>
+          <t>611; 7297</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2454</t>
+          <t>1383; 7910</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2229,17 +2229,17 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>515; 4929</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>614; 7114</t>
+          <t>0; 3103</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>1287; 7930</t>
+          <t>0; 2736</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -2249,17 +2249,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>515; 4971</t>
+          <t>514; 4898</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1008; 7404</t>
+          <t>1383; 7560</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1486; 8155</t>
+          <t>1610; 8693</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2281,42 +2281,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2349,42 +2349,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>669</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>2953</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>2760</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>2939</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>28229</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3283</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>669</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>28229</t>
+          <t>4130</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>674; 7543</t>
+          <t>0; 4235</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>703; 6929</t>
+          <t>1298; 7157</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1120; 6111</t>
+          <t>0; 3402</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1012; 83411</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 4155</t>
+          <t>676; 7227</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1295; 7203</t>
+          <t>690; 6117</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 3560</t>
+          <t>1143; 6257</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>712; 15600</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1653; 9383</t>
+          <t>1828; 8827</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3307; 10771</t>
+          <t>2704; 11012</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1321; 7639</t>
+          <t>1246; 7165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>874; 103726</t>
+          <t>370; 15715</t>
         </is>
       </c>
     </row>
@@ -2494,37 +2494,37 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2557,34 +2557,34 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>3115</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1533</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>3641</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>787</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1191</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>3115</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1778</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2654</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1376; 7846</t>
+          <t>1228; 6272</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5425</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2640,17 +2640,17 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 4454</t>
+          <t>446; 4199</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1229; 6570</t>
+          <t>1400; 7530</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3817</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2660,17 +2660,17 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>541; 4999</t>
+          <t>0; 3810</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3343; 11805</t>
+          <t>3304; 11219</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0; 3899</t>
+          <t>0; 3627</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1155; 6444</t>
+          <t>930; 6119</t>
         </is>
       </c>
     </row>
@@ -2697,42 +2697,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2765,42 +2765,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>3129</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>763</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3434</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1431</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>1413</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>3129</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>763</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>3485</t>
+          <t>3434</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4104</t>
+          <t>1192; 7006</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5171</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 4544</t>
+          <t>0; 3869</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>858; 8297</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1194; 6909</t>
+          <t>0; 3483</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4531</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 3148</t>
+          <t>0; 4735</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>903; 9353</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1802; 8666</t>
+          <t>1792; 7964</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0; 5395</t>
+          <t>0; 5089</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>583; 5612</t>
+          <t>584; 6026</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>984; 8493</t>
+          <t>966; 9204</t>
         </is>
       </c>
     </row>
@@ -2905,34 +2905,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>1</t>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2973,42 +2973,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>610</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>484</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>2098</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>746</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>628</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>1992</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>486</t>
+          <t>484</t>
         </is>
       </c>
     </row>
@@ -3041,62 +3041,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>687; 4833</t>
+          <t>0; 2892</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 3846</t>
+          <t>643; 5514</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 3652</t>
+          <t>0; 3482</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2373</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 2879</t>
+          <t>687; 5524</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>624; 5295</t>
+          <t>0; 3758</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3131</t>
+          <t>0; 3215</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2512</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>704; 5683</t>
+          <t>700; 6325</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>664; 6287</t>
+          <t>661; 6186</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0; 4323</t>
+          <t>0; 3818</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0; 2225</t>
+          <t>0; 2409</t>
         </is>
       </c>
     </row>
@@ -3118,37 +3118,37 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -3186,29 +3186,29 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
           <t>726</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>610</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>620</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>610</t>
+          <t>620</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3254,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3613</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 3138</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3004</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
@@ -3284,7 +3284,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3043</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>0; 3500</t>
+          <t>0; 3876</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>0; 2810</t>
+          <t>0; 3734</t>
         </is>
       </c>
     </row>
@@ -3321,42 +3321,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3389,42 +3389,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>4600</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>672</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>646</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2363</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>4328</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>1423</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>3115</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>4600</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>672</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>646</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>2487</t>
+          <t>1373</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3739</t>
+          <t>3736</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1464; 8678</t>
+          <t>1954; 8883</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 5005</t>
+          <t>0; 3790</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1173; 6451</t>
+          <t>0; 4307</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4307</t>
+          <t>479; 6509</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>1946; 9041</t>
+          <t>1452; 8599</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3416</t>
+          <t>0; 4977</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>0; 3829</t>
+          <t>1144; 6930</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>599; 6701</t>
+          <t>0; 4913</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>4827; 14733</t>
+          <t>4820; 14338</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>672; 5687</t>
+          <t>669; 6257</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>1720; 7853</t>
+          <t>1748; 8214</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>1173; 8453</t>
+          <t>1401; 8292</t>
         </is>
       </c>
     </row>
@@ -3534,37 +3534,37 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -3597,42 +3597,42 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>3146</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>1448</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
           <t>3332</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="I26" s="2" t="inlineStr">
         <is>
           <t>792</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>3146</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1506</t>
+          <t>1448</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1123; 7021</t>
+          <t>1171; 7190</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 3852</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 4016</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5241</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1181; 7197</t>
+          <t>1247; 7474</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3857</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3842</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0; 5686</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>3185; 11339</t>
+          <t>3291; 11840</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0; 4130</t>
+          <t>0; 3089</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>0; 4731</t>
+          <t>0; 3969</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0; 5764</t>
+          <t>0; 5327</t>
         </is>
       </c>
     </row>
@@ -3737,42 +3737,42 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="I28" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -3805,42 +3805,42 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="I29" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>31282</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>16506</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>13613; 28203</t>
+          <t>9852; 23333</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>5181; 16126</t>
+          <t>4738; 14816</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>5434; 15144</t>
+          <t>3160; 12253</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3260; 121356</t>
+          <t>4997; 15865</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>10573; 23863</t>
+          <t>13041; 27491</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>4595; 14072</t>
+          <t>5602; 15733</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3152; 11816</t>
+          <t>5349; 14758</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>5599; 16017</t>
+          <t>3141; 17899</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>26612; 44725</t>
+          <t>26158; 44427</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>12034; 26919</t>
+          <t>12306; 25324</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>9970; 22026</t>
+          <t>9986; 22931</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>12678; 155409</t>
+          <t>9948; 27531</t>
         </is>
       </c>
     </row>
